--- a/micron/dist/20261023_美光模型_v0.3.xlsx
+++ b/micron/dist/20261023_美光模型_v0.3.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="869">
   <si>
     <r>
       <rPr>
@@ -21535,6 +21535,2224 @@
   </si>
   <si>
     <t xml:space="preserve">FY2029 EPS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光歷史財務（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 10-K XBRL</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">macrotrends </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">會計年度底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">會計年度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/B</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">權益 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">庫藏股（成本）</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歸屬淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$B</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">權益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利（虧損年不計）；買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">權益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（權益＋庫藏股）。庫藏股為成本；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底尚未公布，調整每股淨值用 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值（偏低）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">十年倍數與規則值（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底；見頂年 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位、中段中位數、谷底 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：合理倍數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底倍數依循環位置取分位。多個來源時各自取分位再平均、四捨五入到兩位。倍數歷史為輸入（藍字），來源與標記見各表；原放在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/overview/extract.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-23 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">移入）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（主）：十年歷史倍數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年底</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">macrotrends</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（會計年度 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">companiesmarketcap</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（日曆年底，參考不採用）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">標記／說明</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">macrotrends</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（會計年度 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">companiesmarketcap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（日曆年底，參考不採用）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（各來源）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中位數（各來源）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（各來源）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最小（各來源）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最大（各來源）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最小（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最大（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參考 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；不採用的來源）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參考 中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；不採用的來源）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參考 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；不採用的來源）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（主）：規則值</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">循環位置</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現價 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基準</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：見頂（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">見頂年 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底每股淨值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：中段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中段 → 中位數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：谷底（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">谷底 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底每股淨值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（對照）：十年歷史倍數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 10-K </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">換算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 10-K </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">換算：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">虧損年不計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最小（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最大（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（對照）：規則值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：見頂（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：中段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：谷底（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（對照）：十年歷史倍數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 中位數（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最小（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最大（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（對照）：規則值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：見頂（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底調整每股淨值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：中段（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：谷底（買回加回 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底調整每股淨值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -23109,7 +25327,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0%"/>
@@ -23117,6 +25335,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -23227,7 +25446,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -23293,6 +25512,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -23683,12 +25906,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>762</v>
+        <v>838</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>763</v>
+        <v>839</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
@@ -23700,7 +25923,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>764</v>
+        <v>840</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -23712,7 +25935,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>765</v>
+        <v>841</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
@@ -23724,7 +25947,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>766</v>
+        <v>842</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">Mkt!E27</f>
@@ -23736,10 +25959,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>767</v>
+        <v>843</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>768</v>
+        <v>844</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>36</v>
@@ -23770,103 +25993,103 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>769</v>
+        <v>845</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>770</v>
+        <v>846</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>771</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>772</v>
+        <v>848</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>773</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>774</v>
+        <v>850</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>775</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>776</v>
+        <v>852</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>777</v>
+        <v>853</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>778</v>
+        <v>854</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>779</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>780</v>
+        <v>856</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>781</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>782</v>
+        <v>858</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>783</v>
+        <v>859</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>784</v>
+        <v>860</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>785</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>786</v>
+        <v>862</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>787</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>788</v>
+        <v>864</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>789</v>
+        <v>865</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>790</v>
+        <v>866</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>791</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>792</v>
+        <v>868</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>791</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>
@@ -32265,10 +34488,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
@@ -33842,6 +36065,1255 @@
       <c r="G60" s="11" t="n">
         <f aca="false">F60/px-1</f>
         <v>0.0448144626830411</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>740</v>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>-0.276</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>741</v>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>18.621</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>5.089</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>742</v>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>32.294</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>14.135</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>35.881</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>3.221</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>6.313</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>744</v>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>38.996</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>2.687</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>745</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>43.933</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>4.695</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>5.861</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>49.907</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>7.127</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>8.687</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>7.552</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>-5.833</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>45.131</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>7.852</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>0.778</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>54.165</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>7.852</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>8.539</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
+        <v>740</v>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C82" s="14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>741</v>
+      </c>
+      <c r="B83" s="14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C83" s="14" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>742</v>
+      </c>
+      <c r="B84" s="14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C84" s="14" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="B85" s="14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>744</v>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C86" s="14" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>745</v>
+      </c>
+      <c r="B87" s="14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C87" s="14" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="B88" s="14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C88" s="14" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="B89" s="14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C89" s="14" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="B90" s="14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C90" s="14" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="B91" s="14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="B92" s="10" t="n">
+        <f aca="false">PERCENTILE(B82:B91,0.25)</f>
+        <v>1.3</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <f aca="false">PERCENTILE(C82:C91,0.25)</f>
+        <v>1.6875</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B93" s="10" t="n">
+        <f aca="false">MEDIAN(B82:B91)</f>
+        <v>1.75</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <f aca="false">MEDIAN(C82:C91)</f>
+        <v>2.065</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="B94" s="10" t="n">
+        <f aca="false">PERCENTILE(B82:B91,0.75)</f>
+        <v>1.82</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <f aca="false">PERCENTILE(C82:C91,0.75)</f>
+        <v>2.1775</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="B95" s="10" t="n">
+        <f aca="false">MIN(B82:B91)</f>
+        <v>1.22</v>
+      </c>
+      <c r="C95" s="10" t="n">
+        <f aca="false">MIN(C82:C91)</f>
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B96" s="10" t="n">
+        <f aca="false">MAX(B82:B91)</f>
+        <v>2.46</v>
+      </c>
+      <c r="C96" s="10" t="n">
+        <f aca="false">MAX(C82:C91)</f>
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B97" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B92),2)</f>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B98" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B93),2)</f>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B99" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B94),2)</f>
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B100" s="10" t="n">
+        <f aca="false">ROUND(MIN(B95),2)</f>
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B101" s="10" t="n">
+        <f aca="false">ROUND(MAX(B96),2)</f>
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="B102" s="10" t="n">
+        <f aca="false">ROUND(C92,2)</f>
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="B103" s="10" t="n">
+        <f aca="false">ROUND(C93,2)</f>
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="B104" s="10" t="n">
+        <f aca="false">ROUND(C94,2)</f>
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="C108" s="10" t="n">
+        <f aca="false">B97</f>
+        <v>1.3</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <f aca="false">Y!D28</f>
+        <v>207.010352460641</v>
+      </c>
+      <c r="F108" s="17" t="n">
+        <f aca="false">C108*E108</f>
+        <v>269.113458198834</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <f aca="false">F108/px-1</f>
+        <v>-0.752653071508425</v>
+      </c>
+      <c r="H108" s="10" t="n">
+        <f aca="false">px/E108</f>
+        <v>5.25577579607696</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="C109" s="10" t="n">
+        <f aca="false">B98</f>
+        <v>1.75</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <f aca="false">Y!D28</f>
+        <v>207.010352460641</v>
+      </c>
+      <c r="F109" s="17" t="n">
+        <f aca="false">C109*E109</f>
+        <v>362.268116806123</v>
+      </c>
+      <c r="G109" s="15" t="n">
+        <f aca="false">F109/px-1</f>
+        <v>-0.667032980876726</v>
+      </c>
+      <c r="H109" s="10" t="n">
+        <f aca="false">px/E109</f>
+        <v>5.25577579607696</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C110" s="10" t="n">
+        <f aca="false">B99</f>
+        <v>1.82</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <f aca="false">Y!K28</f>
+        <v>268.727668225875</v>
+      </c>
+      <c r="F110" s="17" t="n">
+        <f aca="false">C110*E110</f>
+        <v>489.084356171092</v>
+      </c>
+      <c r="G110" s="15" t="n">
+        <f aca="false">F110/px-1</f>
+        <v>-0.550473937342746</v>
+      </c>
+      <c r="H110" s="10" t="n">
+        <f aca="false">px/E110</f>
+        <v>4.04870852035042</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="5" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>740</v>
+      </c>
+      <c r="B115" s="10" t="str">
+        <f aca="false">IF(E65&gt;0,B65*C65/E65,"")</f>
+        <v/>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>741</v>
+      </c>
+      <c r="B116" s="10" t="n">
+        <f aca="false">IF(E66&gt;0,B66*C66/E66,"")</f>
+        <v>6.51314207113382</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>742</v>
+      </c>
+      <c r="B117" s="10" t="n">
+        <f aca="false">IF(E67&gt;0,B67*C67/E67,"")</f>
+        <v>4.08958330385568</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="B118" s="10" t="n">
+        <f aca="false">IF(E68&gt;0,B68*C68/E68,"")</f>
+        <v>7.55927926500871</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>744</v>
+      </c>
+      <c r="B119" s="10" t="n">
+        <f aca="false">IF(E69&gt;0,B69*C69/E69,"")</f>
+        <v>18.4313062895422</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>745</v>
+      </c>
+      <c r="B120" s="10" t="n">
+        <f aca="false">IF(E70&gt;0,B70*C70/E70,"")</f>
+        <v>13.7173502815219</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="B121" s="10" t="n">
+        <f aca="false">IF(E71&gt;0,B71*C71/E71,"")</f>
+        <v>7.00892598135145</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="B122" s="10" t="str">
+        <f aca="false">IF(E72&gt;0,B72*C72/E72,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="B123" s="10" t="n">
+        <f aca="false">IF(E73&gt;0,B73*C73/E73,"")</f>
+        <v>136.321143958869</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="B124" s="10" t="n">
+        <f aca="false">IF(E74&gt;0,B74*C74/E74,"")</f>
+        <v>15.6043916149432</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="B125" s="10" t="n">
+        <f aca="false">PERCENTILE(B115:B124,0.25)</f>
+        <v>6.88498000379704</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B126" s="10" t="n">
+        <f aca="false">MEDIAN(B115:B124)</f>
+        <v>10.6383147732653</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="B127" s="10" t="n">
+        <f aca="false">PERCENTILE(B115:B124,0.75)</f>
+        <v>16.311120283593</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="B128" s="10" t="n">
+        <f aca="false">MIN(B115:B124)</f>
+        <v>4.08958330385568</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B129" s="10" t="n">
+        <f aca="false">MAX(B115:B124)</f>
+        <v>136.321143958869</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B130" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B125),2)</f>
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B131" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B126),2)</f>
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B132" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B127),2)</f>
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B133" s="10" t="n">
+        <f aca="false">ROUND(MIN(B128),2)</f>
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B134" s="10" t="n">
+        <f aca="false">ROUND(MAX(B129),2)</f>
+        <v>136.32</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="C138" s="10" t="n">
+        <f aca="false">B130</f>
+        <v>6.88</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <f aca="false">Y!D29</f>
+        <v>190.72605328606</v>
+      </c>
+      <c r="F138" s="17" t="n">
+        <f aca="false">C138*E138</f>
+        <v>1312.19524660809</v>
+      </c>
+      <c r="G138" s="15" t="n">
+        <f aca="false">F138/px-1</f>
+        <v>0.206061807544204</v>
+      </c>
+      <c r="H138" s="10" t="n">
+        <f aca="false">px/E138</f>
+        <v>5.70451693019708</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="C139" s="10" t="n">
+        <f aca="false">B131</f>
+        <v>10.64</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <f aca="false">Y!D29</f>
+        <v>190.72605328606</v>
+      </c>
+      <c r="F139" s="17" t="n">
+        <f aca="false">C139*E139</f>
+        <v>2029.32520696368</v>
+      </c>
+      <c r="G139" s="15" t="n">
+        <f aca="false">F139/px-1</f>
+        <v>0.865188609341617</v>
+      </c>
+      <c r="H139" s="10" t="n">
+        <f aca="false">px/E139</f>
+        <v>5.70451693019708</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C140" s="10" t="n">
+        <f aca="false">B132</f>
+        <v>16.31</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <f aca="false">Y!K29</f>
+        <v>100.810402001366</v>
+      </c>
+      <c r="F140" s="17" t="n">
+        <f aca="false">C140*E140</f>
+        <v>1644.21765664228</v>
+      </c>
+      <c r="G140" s="15" t="n">
+        <f aca="false">F140/px-1</f>
+        <v>0.51122946382562</v>
+      </c>
+      <c r="H140" s="10" t="n">
+        <f aca="false">px/E140</f>
+        <v>10.7925370636381</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="s">
+        <v>740</v>
+      </c>
+      <c r="B145" s="10" t="n">
+        <f aca="false">B65*C65/(C65+D65)</f>
+        <v>1.18874055992067</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="s">
+        <v>741</v>
+      </c>
+      <c r="B146" s="10" t="n">
+        <f aca="false">B66*C66/(C66+D66)</f>
+        <v>1.77361836472603</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="s">
+        <v>742</v>
+      </c>
+      <c r="B147" s="10" t="n">
+        <f aca="false">B67*C67/(C67+D67)</f>
+        <v>1.76653301958867</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="B148" s="10" t="n">
+        <f aca="false">B68*C68/(C68+D68)</f>
+        <v>1.22044217687075</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>744</v>
+      </c>
+      <c r="B149" s="10" t="n">
+        <f aca="false">B69*C69/(C69+D69)</f>
+        <v>1.16553905532936</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>745</v>
+      </c>
+      <c r="B150" s="10" t="n">
+        <f aca="false">B70*C70/(C70+D70)</f>
+        <v>1.65331475693016</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="B151" s="10" t="n">
+        <f aca="false">B71*C71/(C71+D71)</f>
+        <v>1.0675481291861</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="B152" s="10" t="n">
+        <f aca="false">B72*C72/(C72+D72)</f>
+        <v>1.46861743303917</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="B153" s="10" t="n">
+        <f aca="false">B73*C73/(C73+D73)</f>
+        <v>2.00173357492026</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="B154" s="10" t="n">
+        <f aca="false">B74*C74/(C74+D74)</f>
+        <v>2.14853830401342</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="B155" s="10" t="n">
+        <f aca="false">PERCENTILE(B145:B154,0.25)</f>
+        <v>1.19666596415819</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B156" s="10" t="n">
+        <f aca="false">MEDIAN(B145:B154)</f>
+        <v>1.56096609498467</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="B157" s="10" t="n">
+        <f aca="false">PERCENTILE(B145:B154,0.75)</f>
+        <v>1.77184702844169</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="B158" s="10" t="n">
+        <f aca="false">MIN(B145:B154)</f>
+        <v>1.0675481291861</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B159" s="10" t="n">
+        <f aca="false">MAX(B145:B154)</f>
+        <v>2.14853830401342</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B160" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B155),2)</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B161" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B156),2)</f>
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B162" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B157),2)</f>
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B163" s="10" t="n">
+        <f aca="false">ROUND(MIN(B158),2)</f>
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B164" s="10" t="n">
+        <f aca="false">ROUND(MAX(B159),2)</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="C168" s="10" t="n">
+        <f aca="false">B160</f>
+        <v>1.2</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <f aca="false">(Y!D25+$D$74+Y!D24)/Y!D27*1000</f>
+        <v>333.694278898784</v>
+      </c>
+      <c r="F168" s="17" t="n">
+        <f aca="false">C168*E168</f>
+        <v>400.43313467854</v>
+      </c>
+      <c r="G168" s="15" t="n">
+        <f aca="false">F168/px-1</f>
+        <v>-0.631954839449871</v>
+      </c>
+      <c r="H168" s="10" t="n">
+        <f aca="false">px/E168</f>
+        <v>3.26046944403866</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="C169" s="10" t="n">
+        <f aca="false">B161</f>
+        <v>1.56</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <f aca="false">(Y!D25+$D$74+Y!D24)/Y!D27*1000</f>
+        <v>333.694278898784</v>
+      </c>
+      <c r="F169" s="17" t="n">
+        <f aca="false">C169*E169</f>
+        <v>520.563075082103</v>
+      </c>
+      <c r="G169" s="15" t="n">
+        <f aca="false">F169/px-1</f>
+        <v>-0.521541291284832</v>
+      </c>
+      <c r="H169" s="10" t="n">
+        <f aca="false">px/E169</f>
+        <v>3.26046944403866</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C170" s="10" t="n">
+        <f aca="false">B162</f>
+        <v>1.77</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <f aca="false">(Y!K25+$D$74+Y!J24+Y!K24)/Y!K27*1000</f>
+        <v>451.048267170137</v>
+      </c>
+      <c r="F170" s="17" t="n">
+        <f aca="false">C170*E170</f>
+        <v>798.355432891143</v>
+      </c>
+      <c r="G170" s="15" t="n">
+        <f aca="false">F170/px-1</f>
+        <v>-0.266217433004464</v>
+      </c>
+      <c r="H170" s="10" t="n">
+        <f aca="false">px/E170</f>
+        <v>2.41215869606612</v>
       </c>
     </row>
   </sheetData>
@@ -33869,24 +37341,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>734</v>
+        <v>810</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>735</v>
+        <v>811</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>736</v>
+        <v>812</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>737</v>
+        <v>813</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>738</v>
+        <v>814</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>739</v>
+        <v>815</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33906,7 +37378,7 @@
         <v>684</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>740</v>
+        <v>816</v>
       </c>
       <c r="C5" s="13" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -33926,7 +37398,7 @@
         <v>684</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>741</v>
+        <v>817</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -33946,7 +37418,7 @@
         <v>684</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>742</v>
+        <v>818</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -33966,7 +37438,7 @@
         <v>684</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>743</v>
+        <v>819</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -33986,7 +37458,7 @@
         <v>684</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>744</v>
+        <v>820</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -34006,7 +37478,7 @@
         <v>684</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>745</v>
+        <v>821</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -34038,7 +37510,7 @@
         <v>688</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>740</v>
+        <v>816</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -34058,7 +37530,7 @@
         <v>688</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>741</v>
+        <v>817</v>
       </c>
       <c r="C14" s="13" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -34078,7 +37550,7 @@
         <v>688</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>742</v>
+        <v>818</v>
       </c>
       <c r="C15" s="13" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -34098,7 +37570,7 @@
         <v>688</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>743</v>
+        <v>819</v>
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -34118,7 +37590,7 @@
         <v>688</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>744</v>
+        <v>820</v>
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -34138,7 +37610,7 @@
         <v>688</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>745</v>
+        <v>821</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -34170,7 +37642,7 @@
         <v>691</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>740</v>
+        <v>816</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -34190,7 +37662,7 @@
         <v>691</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>741</v>
+        <v>817</v>
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -34210,7 +37682,7 @@
         <v>691</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>742</v>
+        <v>818</v>
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -34230,7 +37702,7 @@
         <v>691</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>743</v>
+        <v>819</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -34250,7 +37722,7 @@
         <v>691</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>744</v>
+        <v>820</v>
       </c>
       <c r="C25" s="13" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -34270,7 +37742,7 @@
         <v>691</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>745</v>
+        <v>821</v>
       </c>
       <c r="C26" s="13" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -34302,7 +37774,7 @@
         <v>692</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>740</v>
+        <v>816</v>
       </c>
       <c r="C29" s="13" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -34322,7 +37794,7 @@
         <v>692</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>741</v>
+        <v>817</v>
       </c>
       <c r="C30" s="13" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -34342,7 +37814,7 @@
         <v>692</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>742</v>
+        <v>818</v>
       </c>
       <c r="C31" s="13" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -34362,7 +37834,7 @@
         <v>692</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>743</v>
+        <v>819</v>
       </c>
       <c r="C32" s="13" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -34382,7 +37854,7 @@
         <v>692</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>744</v>
+        <v>820</v>
       </c>
       <c r="C33" s="13" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -34402,7 +37874,7 @@
         <v>692</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>745</v>
+        <v>821</v>
       </c>
       <c r="C34" s="13" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -34419,7 +37891,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>746</v>
+        <v>822</v>
       </c>
     </row>
   </sheetData>
@@ -34447,7 +37919,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>747</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34455,21 +37927,21 @@
         <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>748</v>
+        <v>824</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>749</v>
+        <v>825</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>750</v>
+        <v>826</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>751</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>752</v>
+        <v>828</v>
       </c>
       <c r="B4" s="13" t="n">
         <f aca="false">Y!C4</f>
@@ -34488,7 +37960,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>753</v>
+        <v>829</v>
       </c>
       <c r="B5" s="13" t="n">
         <f aca="false">Y!D4</f>
@@ -34502,12 +37974,12 @@
         <v>-0.0263064385270931</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>754</v>
+        <v>830</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>755</v>
+        <v>831</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">Y!D20</f>
@@ -34521,12 +37993,12 @@
         <v>-0.0415922755838437</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>756</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>757</v>
+        <v>833</v>
       </c>
       <c r="B7" s="13" t="n">
         <f aca="false">Y!E4</f>
@@ -34540,12 +38012,12 @@
         <v>-0.0681646294175106</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>758</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>759</v>
+        <v>835</v>
       </c>
       <c r="B8" s="13" t="n">
         <f aca="false">Y!E20</f>
@@ -34559,12 +38031,12 @@
         <v>-0.111304258340884</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>756</v>
+        <v>832</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>760</v>
+        <v>836</v>
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">Y!D4/4</f>
@@ -34578,7 +38050,7 @@
         <v>0.0884785748172741</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>761</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
